--- a/product_upload/packages/61/file.xlsx
+++ b/product_upload/packages/61/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -824,6 +829,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>LOTEVAN 10/160MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-CD868869A00A</t>
         </is>
       </c>
@@ -847,7 +857,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1002,6 +1012,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>LOSEC MUPS 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-8361FCD88AFF</t>
         </is>
       </c>
@@ -1025,7 +1040,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1184,6 +1199,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>LOSEC MUPS 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-E3B67823E3DD</t>
         </is>
       </c>
@@ -1207,7 +1227,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Turkey</t>
+          <t>TR</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1366,6 +1386,11 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>LOPRESOR 100MG TAB</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-81B845873BA8</t>
         </is>
       </c>
@@ -1389,7 +1414,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1544,6 +1569,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>MARVELON TAB</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-01BB6ADC91E7</t>
         </is>
       </c>
@@ -1567,7 +1597,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1730,6 +1760,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>MEDACIN -T 1% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-3AAEC26686B3</t>
         </is>
       </c>
@@ -1753,7 +1788,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1912,6 +1947,11 @@
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>LECITAL 20MG F.C. CAPLETS</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-D06CE63DA62C</t>
         </is>
       </c>
@@ -1935,7 +1975,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2090,6 +2130,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>LATANOCOM OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-5417F1B1DC2A</t>
         </is>
       </c>
@@ -2113,7 +2158,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2268,6 +2313,11 @@
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>LAMICTAL</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-636C95C30B39</t>
         </is>
       </c>
@@ -2291,7 +2341,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2446,6 +2496,11 @@
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>LAMICTAL</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-04EA4C0099B0</t>
         </is>
       </c>
@@ -2469,7 +2524,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2630,6 +2685,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>LANTUS SOLOSTAR 100I.U-ML DISPOSABLE PEN</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-0856B99DE9D1</t>
         </is>
       </c>
@@ -2653,7 +2713,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2812,6 +2872,11 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>LIVIAL 2.5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-7055E3103128</t>
         </is>
       </c>
@@ -2835,7 +2900,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -2994,6 +3059,11 @@
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>LOHIST 5 MG-5 ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-0F06A90E3BE9</t>
         </is>
       </c>
@@ -3017,7 +3087,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Oman</t>
+          <t>OM</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3176,6 +3246,11 @@
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>LOHIST 10 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-A53BCB66077C</t>
         </is>
       </c>
@@ -3199,7 +3274,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3358,6 +3433,11 @@
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>LOFRAL 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-B8FCEBC00A33</t>
         </is>
       </c>
@@ -3381,7 +3461,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3540,6 +3620,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>LOFRAL 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-AD05A5F05C83</t>
         </is>
       </c>
@@ -3563,7 +3648,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3718,6 +3803,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t>LOCOID OINT 0.1%</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-89EBBC1DE223</t>
         </is>
       </c>
@@ -3741,7 +3831,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3896,6 +3986,11 @@
       <c r="AS19" t="inlineStr"/>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>LISINO 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-B025DB6B9BB6</t>
         </is>
       </c>
@@ -3919,7 +4014,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4074,6 +4169,11 @@
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>LISINO 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-CC03B4E6195A</t>
         </is>
       </c>
@@ -4097,7 +4197,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4252,6 +4352,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>NEORIN 5MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-61A72C91B100</t>
         </is>
       </c>
@@ -4275,7 +4380,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4430,6 +4535,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>NEURO- B FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-4F279FFBB581</t>
         </is>
       </c>
@@ -4453,7 +4563,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4612,6 +4722,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>NEUROPLEX 400MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-A755DAA37569</t>
         </is>
       </c>
@@ -4635,7 +4750,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4790,6 +4905,11 @@
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>NEUROPLEX 300MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-6952ABF9D7B0</t>
         </is>
       </c>
@@ -4813,7 +4933,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4972,6 +5092,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>NOMAL 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-053DC7CD5BEC</t>
         </is>
       </c>
@@ -4995,7 +5120,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5150,6 +5275,11 @@
       </c>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>MINIMS ARTIFICIAL TEARS</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-C93041DC9E7D</t>
         </is>
       </c>
@@ -5173,7 +5303,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Switzerland</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5336,6 +5466,11 @@
       </c>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>MONUROL 3G SACHETS</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-CCE139F662CA</t>
         </is>
       </c>
@@ -5359,7 +5494,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5514,6 +5649,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>MUCOSOLVAN 30MG-5ML ORAL LIQUID</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-115AD1DFEDD2</t>
         </is>
       </c>
@@ -5537,7 +5677,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5696,6 +5836,11 @@
       </c>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>MOFETAB 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-1B7E006FC5E6</t>
         </is>
       </c>
@@ -5719,7 +5864,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -5874,6 +6019,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>UNITUM 5% GEL</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-9EB0FC553890</t>
         </is>
       </c>
@@ -5897,7 +6047,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6052,6 +6202,11 @@
       </c>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>V-2 PLUS CAPS</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-69C0E4A5270F</t>
         </is>
       </c>
@@ -6075,7 +6230,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6234,6 +6389,11 @@
       </c>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>TYMER 0.3% EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-4A31A0DDFCCE</t>
         </is>
       </c>
@@ -6257,7 +6417,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6420,6 +6580,11 @@
       </c>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>TRIVASTAL RETARD 50MG TAB</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-CCA1B0E0940B</t>
         </is>
       </c>
@@ -6443,7 +6608,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6608,6 +6773,11 @@
       </c>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>VICTOZA 6MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-ECF404CE6BA6</t>
         </is>
       </c>
@@ -6631,7 +6801,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -6790,6 +6960,11 @@
       <c r="AS35" t="inlineStr"/>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>TRIPOFED DM SYRUP</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-DB58A553AAEA</t>
         </is>
       </c>
@@ -6813,7 +6988,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -6976,6 +7151,11 @@
       <c r="AS36" t="inlineStr"/>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>TEARS NATURALE FREE</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-494AEBCB9C44</t>
         </is>
       </c>
@@ -6999,7 +7179,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7154,6 +7334,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>TENORETIC TAB</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-2F6DC0CD452F</t>
         </is>
       </c>
@@ -7177,7 +7362,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7332,6 +7517,11 @@
       <c r="AS38" t="inlineStr"/>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>TABUVAN 160 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-A0AA8B54C98C</t>
         </is>
       </c>
@@ -7355,7 +7545,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7510,6 +7700,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>TABUNEX 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-8E9C9EF63FAA</t>
         </is>
       </c>
@@ -7533,7 +7728,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7688,6 +7883,11 @@
       <c r="AS40" t="inlineStr"/>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>TABUVAN 320 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-533CA580774C</t>
         </is>
       </c>
@@ -7711,7 +7911,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -7870,6 +8070,11 @@
       </c>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>TABUVAN 40 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-33A60A1977F2</t>
         </is>
       </c>
@@ -7893,7 +8098,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8048,6 +8253,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>TABUVAN 80 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-F9B9F89A7102</t>
         </is>
       </c>
@@ -8071,7 +8281,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8228,6 +8438,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>TRAJENTA 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-5C1DB5A0EC07</t>
         </is>
       </c>
@@ -8251,7 +8466,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8410,6 +8625,11 @@
       </c>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>TOPRAZOLE 20MG ENTERIC COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-0EB82F02A012</t>
         </is>
       </c>
@@ -8433,7 +8653,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8596,6 +8816,11 @@
       </c>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>ZELAX 20MG FILM COATED CAPLET</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-90ED0595C9BA</t>
         </is>
       </c>
@@ -8619,7 +8844,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -8778,6 +9003,11 @@
       <c r="AS46" t="inlineStr"/>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>ZELAX 10MG FILM COATED CAPLET</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-F869A4FA7703</t>
         </is>
       </c>
@@ -8801,7 +9031,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -8960,6 +9190,11 @@
       </c>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>ZIAGEN 300MG TAB</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-9D2F545F5EE9</t>
         </is>
       </c>
@@ -8983,7 +9218,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9142,6 +9377,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>ZESTRIL 5MG TAB</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-A927C01B2C57</t>
         </is>
       </c>
@@ -9165,7 +9405,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9324,6 +9564,11 @@
       </c>
       <c r="AT49" t="inlineStr">
         <is>
+          <t>ZESTRIL 20MG TAB</t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-AE83E0D0E64C</t>
         </is>
       </c>
@@ -9347,7 +9592,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9502,6 +9747,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>ZESTRIL 10MG TAB</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-B831B9A19360</t>
         </is>
       </c>
@@ -9525,7 +9775,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -9680,6 +9930,11 @@
       <c r="AS51" t="inlineStr"/>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>ZOMIDOR 2% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-B89C63EB89B3</t>
         </is>
       </c>
@@ -9703,7 +9958,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -9854,6 +10109,11 @@
       <c r="AS52" t="inlineStr"/>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>ZOVIRAX 200MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-259FB9B1ABC4</t>
         </is>
       </c>
@@ -9877,7 +10137,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10032,6 +10292,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>ZOVIRAX</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-C19D7BB58440</t>
         </is>
       </c>
@@ -10055,7 +10320,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10214,6 +10479,11 @@
       </c>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>ZOVIRAX</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-3333240C39A0</t>
         </is>
       </c>
@@ -10237,7 +10507,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10392,6 +10662,11 @@
       <c r="AS55" t="inlineStr"/>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>VOLTIC 25MG E.C. TABLET</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-1EBFDC901E3B</t>
         </is>
       </c>
@@ -10415,7 +10690,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -10574,6 +10849,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>WATER FOR INJ AMP</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-92E1D06F570A</t>
         </is>
       </c>
@@ -10597,7 +10877,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -10752,6 +11032,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>VITANERVE F.C TAB</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-08D802A6A1FF</t>
         </is>
       </c>
@@ -10775,7 +11060,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -10932,6 +11217,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>XERACTAN 20 MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-69BE28BA7738</t>
         </is>
       </c>
@@ -10955,7 +11245,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11114,6 +11404,11 @@
       </c>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>XERACTAN 10 MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-6EE73CC76E3D</t>
         </is>
       </c>
@@ -11137,7 +11432,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11292,6 +11587,11 @@
       <c r="AS60" t="inlineStr"/>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>WINEX 100MG\5ML ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-D2F555BEDBD3</t>
         </is>
       </c>
@@ -11315,7 +11615,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -11470,6 +11770,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>WAXSOL</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-BDECBEB8D775</t>
         </is>
       </c>
@@ -11493,7 +11798,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -11648,6 +11953,11 @@
       <c r="AS62" t="inlineStr"/>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>XALATAN 50MCG\ML EYE DROP</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-A8E2C795126D</t>
         </is>
       </c>
@@ -11671,7 +11981,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -11834,6 +12144,11 @@
       <c r="AS63" t="inlineStr"/>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>XANAX 0.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-03A138E854B9</t>
         </is>
       </c>
@@ -11857,7 +12172,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12020,6 +12335,11 @@
       <c r="AS64" t="inlineStr"/>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>XANAX 0.25 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-7C09B972F7E1</t>
         </is>
       </c>
@@ -12043,7 +12363,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12200,6 +12520,11 @@
       <c r="AS65" t="inlineStr"/>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>XEFO 8MG TAB</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-EDA5676FB75A</t>
         </is>
       </c>
@@ -12223,7 +12548,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12382,6 +12707,11 @@
       <c r="AS66" t="inlineStr"/>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>XANAX 1 MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-38625D0D253B</t>
         </is>
       </c>
@@ -12405,7 +12735,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -12564,6 +12894,11 @@
       </c>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>ROLIP ointment</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-A384A5B5EB74</t>
         </is>
       </c>
@@ -12587,7 +12922,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -12742,6 +13077,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>RISIDONE 1MG/1ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-3840A19494AF</t>
         </is>
       </c>
@@ -12765,7 +13105,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -12924,6 +13264,11 @@
       </c>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>RIFACIN 300 MG CAPS</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-2A0EF2FB9981</t>
         </is>
       </c>
@@ -12947,7 +13292,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13110,6 +13455,11 @@
       <c r="AS70" t="inlineStr"/>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>SARTAN 100 mg Film coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-F3E1C9BD5A8C</t>
         </is>
       </c>
@@ -13133,7 +13483,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13300,6 +13650,11 @@
       </c>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>SARTAN 50 mg Film coated Tablets</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-F7282CB81CF0</t>
         </is>
       </c>
@@ -13323,7 +13678,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -13490,6 +13845,11 @@
       </c>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>ROZEX GEL 0.75% W-W</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-DF08D1BCD6FA</t>
         </is>
       </c>
@@ -13513,7 +13873,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -13672,6 +14032,11 @@
       <c r="AS73" t="inlineStr"/>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>SALBULASE 2MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-F366DB3803C2</t>
         </is>
       </c>
@@ -13695,7 +14060,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -13850,6 +14215,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>RIFACIN 150MG CAP.</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-9BACF9490ABF</t>
         </is>
       </c>
@@ -13873,7 +14243,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14032,6 +14402,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>RIDON 4 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-25FC2B3EE998</t>
         </is>
       </c>
@@ -14055,7 +14430,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14214,6 +14589,11 @@
       </c>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>REPADERM GEL</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-FE86708889FA</t>
         </is>
       </c>
@@ -14237,7 +14617,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -14392,6 +14772,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>RENITEC</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-931A99233437</t>
         </is>
       </c>
@@ -14415,7 +14800,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -14574,6 +14959,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>REPADERM GEL</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-128498695D50</t>
         </is>
       </c>
@@ -14597,7 +14987,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -14760,6 +15150,11 @@
       </c>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>REPARIL GEL N</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-265F3AE6754D</t>
         </is>
       </c>
@@ -14783,7 +15178,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -14942,6 +15337,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>REPARIL GEL N</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-43BD3A8880A8</t>
         </is>
       </c>
@@ -14965,7 +15365,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15124,6 +15524,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>RESPAL 4 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-36727A8599D1</t>
         </is>
       </c>
@@ -15147,7 +15552,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -15310,6 +15715,11 @@
       </c>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>RESPAL 2 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-861D26E4506F</t>
         </is>
       </c>
@@ -15333,7 +15743,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -15492,6 +15902,11 @@
       </c>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>RELESTAT 0.05% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-D3F1E757ACB4</t>
         </is>
       </c>
@@ -15515,7 +15930,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15678,6 +16093,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>RELENZA 5MG POWDER FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-44D84997646D</t>
         </is>
       </c>
@@ -15701,7 +16121,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -15852,6 +16272,11 @@
       <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>REFRESH PLUS</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-89D457E680CE</t>
         </is>
       </c>
@@ -15875,7 +16300,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16030,6 +16455,11 @@
       <c r="AS86" t="inlineStr"/>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>RIASERTAL 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-929F1A7E5A53</t>
         </is>
       </c>
@@ -16053,7 +16483,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16208,6 +16638,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>RIDON 2 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-F7B31F960790</t>
         </is>
       </c>
@@ -16231,7 +16666,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16382,6 +16817,11 @@
       <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>RIDON 1 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-FDF17DE07AD5</t>
         </is>
       </c>
@@ -16405,7 +16845,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16564,6 +17004,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>RIAXINE</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-2A918EA696A0</t>
         </is>
       </c>
@@ -16587,7 +17032,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16742,6 +17187,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>RIAGESIC</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-BAAF62462711</t>
         </is>
       </c>
@@ -16765,7 +17215,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -16916,6 +17366,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>RETROVIR CAPS 100MG</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-1F40A3536781</t>
         </is>
       </c>
@@ -16939,7 +17394,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17094,6 +17549,11 @@
       <c r="AS92" t="inlineStr"/>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>RHINATHIOL SYRUP 20MG-ML CHILDREN</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-2CEE0130F006</t>
         </is>
       </c>
@@ -17117,7 +17577,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -17272,6 +17732,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>SPASMEX 30MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-CF9689BB9E0B</t>
         </is>
       </c>
@@ -17295,7 +17760,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -17450,6 +17915,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>STALORAL MITES MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-31A4668D24CA</t>
         </is>
       </c>
@@ -17473,7 +17943,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17632,6 +18102,11 @@
       </c>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>STALORAL MITES INITIAL</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-F262C5BC329F</t>
         </is>
       </c>
@@ -17655,7 +18130,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Kuwait</t>
+          <t>KW</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -17818,6 +18293,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>SODIUM CHLORIDE IRRIGATION 0.9%</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-F9C5D8F293E1</t>
         </is>
       </c>
@@ -17841,7 +18321,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18000,6 +18480,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>SINE-UP SYRUP</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-B1E686C7DF85</t>
         </is>
       </c>
@@ -18023,7 +18508,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -18178,6 +18663,11 @@
       <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>SIMVA 40 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-5B8CC45768A5</t>
         </is>
       </c>
@@ -18201,7 +18691,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -18356,6 +18846,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>SIMVA 20 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-559568FC48D6</t>
         </is>
       </c>
@@ -18379,7 +18874,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -18538,6 +19033,11 @@
       </c>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>SIMVA 10 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-81850B5417C9</t>
         </is>
       </c>
@@ -18561,7 +19061,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -18721,6 +19221,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>SIFROL 0.7MG (EQU. 1.00MG) TAB</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-6AC57479C2F8</t>
         </is>
@@ -18737,7 +19242,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18783,100 +19288,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -18908,7 +19418,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -18923,92 +19433,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-65374</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>437.59</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Diabetic Care</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>619</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19040,7 +19555,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -19055,92 +19570,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-88627</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>82.75</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>620</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19172,7 +19692,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -19187,92 +19707,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-22837</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>156.61</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>621</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19304,7 +19829,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -19319,92 +19844,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-89478</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>384.52</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>622</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19436,7 +19966,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -19451,92 +19981,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-14993</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>38.47</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>623</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19568,7 +20103,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -19583,92 +20118,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-25926</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>481.05</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>624</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19700,7 +20240,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -19715,92 +20255,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-99235</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>379.73</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>625</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19832,7 +20377,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -19847,92 +20392,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-10836</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>95.8</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>626</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19964,7 +20514,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -19979,92 +20529,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-79995</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>477.06</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>627</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20096,7 +20651,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -20111,92 +20666,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-87176</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>371.22</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>628</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20228,7 +20788,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -20243,92 +20803,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-20438</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>400.97</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>629</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20345,7 +20910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20451,6 +21016,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -20486,7 +21061,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -20551,6 +21126,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-8CE7333466B4</t>
         </is>
@@ -20587,7 +21172,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -20652,6 +21237,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-020B788AC3F7</t>
         </is>
@@ -20688,7 +21283,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -20753,6 +21348,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-404DA5CF818C</t>
         </is>
@@ -20789,7 +21394,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -20854,6 +21459,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-4292E685977E</t>
         </is>
@@ -20890,7 +21505,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -20955,6 +21570,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-CFAAD44EE0C5</t>
         </is>
@@ -20991,7 +21616,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -21056,6 +21681,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-ACD561B6889B</t>
         </is>
@@ -21092,7 +21727,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -21157,6 +21792,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-8DE519ACBD3E</t>
         </is>
@@ -21193,7 +21838,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -21258,6 +21903,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-A92C49848ACB</t>
         </is>
@@ -21294,7 +21949,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -21359,6 +22014,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-D3B9B155F99C</t>
         </is>
@@ -21395,7 +22060,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -21460,6 +22125,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-35899F0D0D1C</t>
         </is>
@@ -21496,7 +22171,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -21561,6 +22236,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-A4626C141DB4</t>
         </is>
@@ -21597,7 +22282,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -21662,6 +22347,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-EDB333D44769</t>
         </is>
@@ -21698,7 +22393,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -21763,6 +22458,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-9679D8735F91</t>
         </is>
@@ -21799,7 +22504,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -21864,6 +22569,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-44696AFEA050</t>
         </is>
@@ -21900,7 +22615,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -21965,6 +22680,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-EBC6EE141FF7</t>
         </is>
@@ -22001,7 +22726,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -22066,6 +22791,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-60D81B77EC0D</t>
         </is>
@@ -22102,7 +22837,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -22167,6 +22902,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-A5DCBA839A2B</t>
         </is>
@@ -22203,7 +22948,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -22268,6 +23013,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-D914B4B7B27B</t>
         </is>
@@ -22304,7 +23059,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -22369,6 +23124,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-B70BCD6FBBE1</t>
         </is>
@@ -22405,7 +23170,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -22470,6 +23235,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-A54520D28563</t>
         </is>

--- a/product_upload/packages/61/file.xlsx
+++ b/product_upload/packages/61/file.xlsx
@@ -686,8 +686,16 @@
           <t>3057709917-928-346238078850</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOTEVAN 10/160MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>LOTEVAN 10/160MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -865,8 +873,16 @@
           <t>4588711832-629-932679439500</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOSEC MUPS 20MG TAB</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>LOSEC MUPS 20MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1048,8 +1064,16 @@
           <t>8194628221-823-971680200518</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOSEC MUPS 10 MG TAB</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>LOSEC MUPS 10 MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1235,8 +1259,16 @@
           <t>6981158531-791-437567131283</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOPRESOR 100MG TAB</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>LOPRESOR 100MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1422,8 +1454,16 @@
           <t>3174044554-202-182533866001</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MARVELON TAB</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MARVELON TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
@@ -1605,8 +1645,16 @@
           <t>5977420212-276-889821432070</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MEDACIN -T 1% TOPICAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>MEDACIN -T 1% TOPICAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1796,8 +1844,16 @@
           <t>7414049585-705-265761452399</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LECITAL 20MG F.C. CAPLETS</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>LECITAL 20MG F.C. CAPLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
@@ -1983,8 +2039,16 @@
           <t>9533359262-273-587725579380</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LATANOCOM OPHTHALMIC SOLUTION</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>LATANOCOM OPHTHALMIC SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2166,8 +2230,16 @@
           <t>6852378939-088-366183751841</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAMICTAL</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>LAMICTAL detailed description.</t>
+        </is>
+      </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
@@ -2349,8 +2421,16 @@
           <t>9846875109-244-541878296707</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LAMICTAL</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>LAMICTAL detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2532,8 +2612,16 @@
           <t>4661096876-812-950324576509</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LANTUS SOLOSTAR 100I.U-ML DISPOSABLE PEN</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>LANTUS SOLOSTAR 100I.U-ML DISPOSABLE PEN detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>COOPER PHARMA</t>
@@ -2721,8 +2809,16 @@
           <t>6627074859-188-789754376789</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LIVIAL 2.5MG TAB</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>LIVIAL 2.5MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
@@ -2908,8 +3004,16 @@
           <t>9287875649-984-319549692589</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOHIST 5 MG-5 ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>LOHIST 5 MG-5 ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
@@ -3095,8 +3199,16 @@
           <t>8338203807-034-377415335921</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOHIST 10 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>LOHIST 10 MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3282,8 +3394,16 @@
           <t>9118454490-875-851526384458</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOFRAL 5MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>LOFRAL 5MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
@@ -3469,8 +3589,16 @@
           <t>0734289963-216-639541479560</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOFRAL 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>LOFRAL 10MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3656,8 +3784,16 @@
           <t>1570654801-550-339785402798</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LOCOID OINT 0.1%</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>LOCOID OINT 0.1% detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3839,8 +3975,16 @@
           <t>1082152102-437-925915635166</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LISINO 5MG TABLET</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>LISINO 5MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4022,8 +4166,16 @@
           <t>8865234811-506-956294231944</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ LISINO 10MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>LISINO 10MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4205,8 +4357,16 @@
           <t>8223117782-509-935430628957</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEORIN 5MG F.C. TABLET</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>NEORIN 5MG F.C. TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4388,8 +4548,16 @@
           <t>0895780085-048-619720094379</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEURO- B FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NEURO- B FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4571,8 +4739,16 @@
           <t>5926759309-602-779201679233</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUROPLEX 400MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NEUROPLEX 400MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
@@ -4758,8 +4934,16 @@
           <t>9125831592-436-025611480266</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NEUROPLEX 300MG CAPSULES</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>NEUROPLEX 300MG CAPSULES detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
@@ -4941,8 +5125,16 @@
           <t>0412284057-367-785262983953</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOMAL 50 MG CAPSULE</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>NOMAL 50 MG CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
@@ -5128,8 +5320,16 @@
           <t>0373205335-327-661852762285</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MINIMS ARTIFICIAL TEARS</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>MINIMS ARTIFICIAL TEARS detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
@@ -5311,8 +5511,16 @@
           <t>0752243476-211-156608640621</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MONUROL 3G SACHETS</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>MONUROL 3G SACHETS detailed description.</t>
+        </is>
+      </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
@@ -5502,8 +5710,16 @@
           <t>2288135762-739-556565116687</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MUCOSOLVAN 30MG-5ML ORAL LIQUID</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>MUCOSOLVAN 30MG-5ML ORAL LIQUID detailed description.</t>
+        </is>
+      </c>
       <c r="I28" t="n">
         <v>0</v>
       </c>
@@ -5685,8 +5901,16 @@
           <t>9884561617-264-331425551028</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOFETAB 500 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>MOFETAB 500 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I29" t="n">
         <v>0</v>
       </c>
@@ -5872,8 +6096,16 @@
           <t>0126259563-652-603900936639</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ UNITUM 5% GEL</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>UNITUM 5% GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
@@ -6055,8 +6287,16 @@
           <t>7803991628-404-250218189308</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ V-2 PLUS CAPS</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>V-2 PLUS CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
@@ -6238,8 +6478,16 @@
           <t>4475950622-396-708606791722</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TYMER 0.3% EYE DROP</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>TYMER 0.3% EYE DROP detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6425,8 +6673,16 @@
           <t>5678593828-624-921576438613</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRIVASTAL RETARD 50MG TAB</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>TRIVASTAL RETARD 50MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6616,8 +6872,16 @@
           <t>2449070959-177-577720669195</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VICTOZA 6MG/ML SOLUTION FOR INJECTION</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>VICTOZA 6MG/ML SOLUTION FOR INJECTION detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>Saudi Biotechnology Manufacturing Co</t>
@@ -6809,8 +7073,16 @@
           <t>8635566173-460-790019693220</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRIPOFED DM SYRUP</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>TRIPOFED DM SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7187,8 +7459,16 @@
           <t>5300201237-267-925443821747</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TENORETIC TAB</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>TENORETIC TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="n">
         <v>0</v>
       </c>
@@ -7370,8 +7650,16 @@
           <t>2993206729-945-095970596625</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TABUVAN 160 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>TABUVAN 160 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="n">
         <v>0</v>
       </c>
@@ -7553,8 +7841,16 @@
           <t>6206219286-988-833478593009</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TABUNEX 0.05% NASAL SPRAY</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>TABUNEX 0.05% NASAL SPRAY detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
@@ -7736,8 +8032,16 @@
           <t>9546203316-637-979563476939</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TABUVAN 320 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>TABUVAN 320 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="n">
         <v>0</v>
       </c>
@@ -7919,8 +8223,16 @@
           <t>4689958540-582-291383101563</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TABUVAN 40 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>TABUVAN 40 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8106,8 +8418,16 @@
           <t>5692436105-638-044932620474</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TABUVAN 80 MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>TABUVAN 80 MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
@@ -8289,8 +8609,16 @@
           <t>9885474861-327-144238703011</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TRAJENTA 5MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>TRAJENTA 5MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="inlineStr">
         <is>
           <t>TABUK PHARMACEUTICAL MANUFACTURING CO.</t>
@@ -8474,8 +8802,16 @@
           <t>3842249984-190-201367754189</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TOPRAZOLE 20MG ENTERIC COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>TOPRAZOLE 20MG ENTERIC COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -8661,8 +8997,16 @@
           <t>3585871963-069-024295450838</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZELAX 20MG FILM COATED CAPLET</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>ZELAX 20MG FILM COATED CAPLET detailed description.</t>
+        </is>
+      </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
@@ -8852,8 +9196,16 @@
           <t>4649023736-873-150126899984</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZELAX 10MG FILM COATED CAPLET</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>ZELAX 10MG FILM COATED CAPLET detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9039,8 +9391,16 @@
           <t>0658524344-890-696203339300</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZIAGEN 300MG TAB</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>ZIAGEN 300MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9226,8 +9586,16 @@
           <t>8971537234-027-189218018105</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZESTRIL 5MG TAB</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>ZESTRIL 5MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -9413,8 +9781,16 @@
           <t>0062693700-555-462623388934</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZESTRIL 20MG TAB</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>ZESTRIL 20MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
@@ -9600,8 +9976,16 @@
           <t>4703576487-267-288979873954</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZESTRIL 10MG TAB</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>ZESTRIL 10MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I50" t="n">
         <v>0</v>
       </c>
@@ -9783,8 +10167,16 @@
           <t>2076850479-668-498632315264</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOMIDOR 2% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>ZOMIDOR 2% EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I51" t="n">
         <v>0</v>
       </c>
@@ -9966,8 +10358,16 @@
           <t>0497361508-422-197428084515</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOVIRAX 200MG\5ML SUSP</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ZOVIRAX 200MG\5ML SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I52" t="n">
         <v>0</v>
       </c>
@@ -10145,8 +10545,16 @@
           <t>5333211791-720-012452752082</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOVIRAX</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>ZOVIRAX detailed description.</t>
+        </is>
+      </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
@@ -10328,8 +10736,16 @@
           <t>3478472099-246-324971712645</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ZOVIRAX</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>ZOVIRAX detailed description.</t>
+        </is>
+      </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
@@ -10515,8 +10931,16 @@
           <t>1113491505-543-056778486073</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VOLTIC 25MG E.C. TABLET</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>VOLTIC 25MG E.C. TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
@@ -10698,8 +11122,16 @@
           <t>0946105620-623-161599650687</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WATER FOR INJ AMP</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>WATER FOR INJ AMP detailed description.</t>
+        </is>
+      </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
@@ -10885,8 +11317,16 @@
           <t>2563345218-737-907027483704</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VITANERVE F.C TAB</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>VITANERVE F.C TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
@@ -11068,8 +11508,16 @@
           <t>9113261747-865-395349166364</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XERACTAN 20 MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>XERACTAN 20 MG SOFT GELATIN CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I58" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -11253,8 +11701,16 @@
           <t>2711436667-005-692104489281</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XERACTAN 10 MG SOFT GELATIN CAPSULE</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>XERACTAN 10 MG SOFT GELATIN CAPSULE detailed description.</t>
+        </is>
+      </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
@@ -11440,8 +11896,16 @@
           <t>6935454988-270-390653932318</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WINEX 100MG\5ML ORAL SUSP</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>WINEX 100MG\5ML ORAL SUSP detailed description.</t>
+        </is>
+      </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
@@ -11623,8 +12087,16 @@
           <t>3488557050-815-916933751702</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ WAXSOL</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>WAXSOL detailed description.</t>
+        </is>
+      </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
@@ -11806,8 +12278,16 @@
           <t>8215752783-028-265147379900</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XALATAN 50MCG\ML EYE DROP</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>XALATAN 50MCG\ML EYE DROP detailed description.</t>
+        </is>
+      </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
@@ -11989,8 +12469,16 @@
           <t>1682879266-082-477074323670</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XANAX 0.5 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>XANAX 0.5 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
@@ -12180,8 +12668,16 @@
           <t>4127621926-930-063076893530</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XANAX 0.25 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>XANAX 0.25 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -12371,8 +12867,16 @@
           <t>1248155691-667-836182519025</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XEFO 8MG TAB</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>XEFO 8MG TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>Jazeera Pharmaceutical Industries (JPI)</t>
@@ -12556,8 +13060,16 @@
           <t>4590266244-269-808771012748</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ XANAX 1 MG TABLET</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>XANAX 1 MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -12743,8 +13255,16 @@
           <t>1748094745-825-049715324110</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROLIP ointment</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>ROLIP ointment detailed description.</t>
+        </is>
+      </c>
       <c r="I67" t="n">
         <v>0</v>
       </c>
@@ -12930,8 +13450,16 @@
           <t>9370467241-750-796342684072</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RISIDONE 1MG/1ML ORAL SOLUTION</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>RISIDONE 1MG/1ML ORAL SOLUTION detailed description.</t>
+        </is>
+      </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
@@ -13113,8 +13641,16 @@
           <t>1621915880-234-343155727223</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIFACIN 300 MG CAPS</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>RIFACIN 300 MG CAPS detailed description.</t>
+        </is>
+      </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
@@ -13300,8 +13836,16 @@
           <t>3931298524-961-490802621742</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SARTAN 100 mg Film coated Tablets</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>SARTAN 100 mg Film coated Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -13491,8 +14035,16 @@
           <t>6654920130-886-198119476183</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SARTAN 50 mg Film coated Tablets</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>SARTAN 50 mg Film coated Tablets detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -13686,8 +14238,16 @@
           <t>2616294838-928-974569470687</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ROZEX GEL 0.75% W-W</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ROZEX GEL 0.75% W-W detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -13881,8 +14441,16 @@
           <t>8620276122-792-281044912837</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SALBULASE 2MG-5ML SYRUP</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>SALBULASE 2MG-5ML SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -14068,8 +14636,16 @@
           <t>5929732194-668-943169997585</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIFACIN 150MG CAP.</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>RIFACIN 150MG CAP. detailed description.</t>
+        </is>
+      </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
@@ -14251,8 +14827,16 @@
           <t>9849296493-289-353004128388</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIDON 4 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>RIDON 4 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
@@ -14438,8 +15022,16 @@
           <t>0795761015-038-418122295421</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr"/>
-      <c r="H76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REPADERM GEL</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>REPADERM GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
@@ -14625,8 +15217,16 @@
           <t>2457899625-628-825773032151</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RENITEC</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>RENITEC detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -14808,8 +15408,16 @@
           <t>9661744511-041-447663580085</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REPADERM GEL</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>REPADERM GEL detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -14995,8 +15603,16 @@
           <t>3562684303-557-102203927342</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr"/>
-      <c r="H79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REPARIL GEL N</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>REPARIL GEL N detailed description.</t>
+        </is>
+      </c>
       <c r="I79" t="n">
         <v>0</v>
       </c>
@@ -15186,8 +15802,16 @@
           <t>3988982497-419-773012201653</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REPARIL GEL N</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>REPARIL GEL N detailed description.</t>
+        </is>
+      </c>
       <c r="I80" t="n">
         <v>0</v>
       </c>
@@ -15373,8 +15997,16 @@
           <t>4155958272-390-036112920409</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr"/>
-      <c r="H81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESPAL 4 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>RESPAL 4 MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I81" t="n">
         <v>0</v>
       </c>
@@ -15560,8 +16192,16 @@
           <t>9185915092-319-489143010997</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RESPAL 2 MG TABLETS</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>RESPAL 2 MG TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -15751,8 +16391,16 @@
           <t>4064320508-753-239092710722</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RELESTAT 0.05% EYE DROPS</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>RELESTAT 0.05% EYE DROPS detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -15938,8 +16586,16 @@
           <t>1864978719-297-088180680975</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RELENZA 5MG POWDER FOR INHALATION</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>RELENZA 5MG POWDER FOR INHALATION detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16129,8 +16785,16 @@
           <t>9822100608-435-754985180055</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ REFRESH PLUS</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>REFRESH PLUS detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -16308,8 +16972,16 @@
           <t>1047206820-840-330735155765</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr"/>
-      <c r="H86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIASERTAL 50 mg film-coated tablet</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>RIASERTAL 50 mg film-coated tablet detailed description.</t>
+        </is>
+      </c>
       <c r="I86" t="n">
         <v>0</v>
       </c>
@@ -16491,8 +17163,16 @@
           <t>1459418984-397-313836249734</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIDON 2 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>RIDON 2 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -16674,8 +17354,16 @@
           <t>8154218576-138-602139701775</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIDON 1 MG FILM COATED TABLETS</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>RIDON 1 MG FILM COATED TABLETS detailed description.</t>
+        </is>
+      </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
@@ -16853,8 +17541,16 @@
           <t>1104481326-559-487999662366</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr"/>
-      <c r="H89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIAXINE</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>RIAXINE detailed description.</t>
+        </is>
+      </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
@@ -17040,8 +17736,16 @@
           <t>7239956795-640-785593127467</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr"/>
-      <c r="H90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RIAGESIC</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>RIAGESIC detailed description.</t>
+        </is>
+      </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
@@ -17223,8 +17927,16 @@
           <t>2009818580-027-880499557140</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr"/>
-      <c r="H91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RETROVIR CAPS 100MG</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>RETROVIR CAPS 100MG detailed description.</t>
+        </is>
+      </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
@@ -17402,8 +18114,16 @@
           <t>0746729612-868-326565862564</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ RHINATHIOL SYRUP 20MG-ML CHILDREN</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>RHINATHIOL SYRUP 20MG-ML CHILDREN detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="n">
         <v>0</v>
       </c>
@@ -17585,8 +18305,16 @@
           <t>9322442370-166-838228060910</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SPASMEX 30MG FILM COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>SPASMEX 30MG FILM COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
@@ -17768,8 +18496,16 @@
           <t>0409090090-692-244852643475</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STALORAL MITES MAINTENANCE</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>STALORAL MITES MAINTENANCE detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
@@ -17951,8 +18687,16 @@
           <t>6827996716-339-049334116777</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ STALORAL MITES INITIAL</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>STALORAL MITES INITIAL detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -18138,8 +18882,16 @@
           <t>3889569781-309-772471640239</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SODIUM CHLORIDE IRRIGATION 0.9%</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>SODIUM CHLORIDE IRRIGATION 0.9% detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -18329,8 +19081,16 @@
           <t>2647636390-119-726214852113</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr"/>
-      <c r="H97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SINE-UP SYRUP</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>SINE-UP SYRUP detailed description.</t>
+        </is>
+      </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
@@ -18516,8 +19276,16 @@
           <t>7407463741-019-767188283969</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMVA 40 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>SIMVA 40 MG COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I98" t="n">
         <v>0</v>
       </c>
@@ -18699,8 +19467,16 @@
           <t>1175990397-950-562725839027</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMVA 20 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>SIMVA 20 MG COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>
@@ -18882,8 +19658,16 @@
           <t>5723672205-960-180651617692</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr"/>
-      <c r="H100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIMVA 10 MG COATED TABLET</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>SIMVA 10 MG COATED TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
@@ -19069,8 +19853,16 @@
           <t>7727562618-727-941747204860</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ SIFROL 0.7MG (EQU. 1.00MG) TAB</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>SIFROL 0.7MG (EQU. 1.00MG) TAB detailed description.</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
           <t xml:space="preserve">ALPHA PHARMA INDUSTRY </t>

--- a/product_upload/packages/61/file.xlsx
+++ b/product_upload/packages/61/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -21702,7 +21702,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21783,40 +21783,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -21896,38 +21901,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>122.58</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-8CE7333466B4</t>
         </is>
@@ -22007,38 +22017,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>162.23</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-020B788AC3F7</t>
         </is>
@@ -22118,38 +22133,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>66.84999999999999</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-404DA5CF818C</t>
         </is>
@@ -22229,38 +22249,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>320.07</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-4292E685977E</t>
         </is>
@@ -22340,38 +22365,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>471.37</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-CFAAD44EE0C5</t>
         </is>
@@ -22451,38 +22481,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>89.81</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-ACD561B6889B</t>
         </is>
@@ -22562,38 +22597,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>139.38</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-8DE519ACBD3E</t>
         </is>
@@ -22673,38 +22713,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>314.39</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-A92C49848ACB</t>
         </is>
@@ -22784,38 +22829,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>294.59</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-D3B9B155F99C</t>
         </is>
@@ -22895,38 +22945,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>114.57</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-35899F0D0D1C</t>
         </is>
@@ -23006,38 +23061,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>85.37</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-A4626C141DB4</t>
         </is>
@@ -23117,38 +23177,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>401.42</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-EDB333D44769</t>
         </is>
@@ -23228,38 +23293,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>104.81</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-9679D8735F91</t>
         </is>
@@ -23339,38 +23409,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>348.4</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-44696AFEA050</t>
         </is>
@@ -23450,38 +23525,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>438.22</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-EBC6EE141FF7</t>
         </is>
@@ -23561,38 +23641,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>206.16</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-60D81B77EC0D</t>
         </is>
@@ -23672,38 +23757,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>238.97</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-A5DCBA839A2B</t>
         </is>
@@ -23783,38 +23873,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>373.89</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-D914B4B7B27B</t>
         </is>
@@ -23894,38 +23989,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>186.6</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-B70BCD6FBBE1</t>
         </is>
@@ -24005,38 +24105,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>252.63</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-A54520D28563</t>
         </is>
